--- a/RFFilters/5PoleChebyshevComponentValues.xlsx
+++ b/RFFilters/5PoleChebyshevComponentValues.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jconrad/GitHub/PocketFT8Xcvr/RFFilters/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FF3868-2ED1-B649-B690-509CBB577095}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="2360" yWindow="7440" windowWidth="25640" windowHeight="12960" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1"/>
@@ -22,78 +27,60 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
-    <t xml:space="preserve">Five Pole Chebyshev Low-Pass Design</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000 pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.198uH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1300 pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.198 uH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1000pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 dB ripple, peak at ~7.06 mHz.  L1=L2=&gt;20T #30 on T37-6</t>
+    <t>Five Pole Chebyshev Low-Pass Design</t>
+  </si>
+  <si>
+    <t>Band</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>40M</t>
+  </si>
+  <si>
+    <t>1000 pF</t>
+  </si>
+  <si>
+    <t>1.198uH</t>
+  </si>
+  <si>
+    <t>1300 pF</t>
+  </si>
+  <si>
+    <t>1.198 uH</t>
+  </si>
+  <si>
+    <t>1000pF</t>
+  </si>
+  <si>
+    <t>1 dB ripple, peak at ~7.06 mHz.  L1=L2=&gt;20T #30 on T37-6 (12")</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
     <font>
       <sz val="12"/>
@@ -101,13 +88,13 @@
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -122,7 +109,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -130,119 +117,92 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="6">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -295,27 +255,29 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:G6"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="6" min="1" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="54.25"/>
+    <col min="1" max="6" width="11.5" style="1"/>
+    <col min="7" max="7" width="63.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" s="3" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
@@ -338,7 +300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" s="5" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -362,10 +324,9 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup scale="89" orientation="landscape" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
